--- a/resources/templates/standard/H3100-02.xlsx
+++ b/resources/templates/standard/H3100-02.xlsx
@@ -14,7 +14,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>고객 만족 평가 시행 계획서</t>
   </si>
@@ -720,11 +723,13 @@
   </cols>
   <sheetData>
     <row r="1" ht="69.95" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
@@ -744,7 +749,7 @@
     <row r="2" ht="20.1" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="4" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
@@ -766,7 +771,7 @@
     <row r="3" ht="20.1" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="7"/>
       <c r="B3" s="8" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" s="8"/>
       <c r="D3" s="8"/>
@@ -788,7 +793,7 @@
     <row r="4" ht="20.1" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="7"/>
       <c r="B4" s="8" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -810,7 +815,7 @@
     <row r="5" ht="20.1" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="7"/>
       <c r="B5" s="8" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
@@ -852,13 +857,13 @@
     <row r="7" ht="20.1" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="7"/>
       <c r="B7" s="14" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C7" s="14"/>
       <c r="D7" s="14"/>
       <c r="E7" s="14"/>
       <c r="F7" s="14" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G7" s="14"/>
       <c r="H7" s="14"/>
@@ -895,10 +900,10 @@
     </row>
     <row r="9" ht="20.1" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C9" s="14"/>
       <c r="D9" s="14"/>
@@ -920,7 +925,7 @@
     <row r="10" ht="20.1" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="7"/>
       <c r="B10" s="8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
@@ -942,7 +947,7 @@
     <row r="11" ht="20.1" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="7"/>
       <c r="B11" s="8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
@@ -984,7 +989,7 @@
     <row r="13" ht="20.1" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="19"/>
       <c r="B13" s="14" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" s="14"/>
       <c r="D13" s="14"/>
@@ -1006,7 +1011,7 @@
     <row r="14" ht="20.1" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="11"/>
       <c r="B14" s="23" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C14" s="23"/>
       <c r="D14" s="23"/>
@@ -1028,7 +1033,7 @@
     <row r="15" ht="20.1" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="7"/>
       <c r="B15" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" s="8"/>
       <c r="D15" s="8"/>
@@ -1050,7 +1055,7 @@
     <row r="16" ht="20.1" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="7"/>
       <c r="B16" s="17" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C16" s="17"/>
       <c r="D16" s="17"/>
@@ -1252,7 +1257,7 @@
     <row r="26" ht="20.1" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" s="7"/>
       <c r="B26" s="8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
@@ -1293,7 +1298,7 @@
     </row>
     <row r="28" ht="20.1" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" s="25" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B28" s="25"/>
       <c r="C28" s="25"/>
@@ -1342,26 +1347,26 @@
       <c r="F30" s="8"/>
       <c r="G30" s="8"/>
       <c r="H30" s="26" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I30" s="27" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J30" s="27"/>
       <c r="K30" s="27" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L30" s="27"/>
       <c r="M30" s="27" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N30" s="27"/>
       <c r="O30" s="27" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P30" s="27"/>
       <c r="Q30" s="27" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R30" s="27"/>
     </row>
